--- a/assets/aGTM-Events-v1.5.xlsx
+++ b/assets/aGTM-Events-v1.5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="aGTM Events" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Page &amp; Device Info" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="aGTM Variables" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="aGTM Events" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Page &amp; Device Info" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="aGTM Variables" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Legend" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P12" s="5" t="inlineStr">
         <is>
-          <t>ONLY on "JS Error": error counter (max. 5 are pushed, 100 counted)</t>
+          <t>ONLY on "JS Error": error counter (max. 5 are pushed, 100 counted); no "JS Error" events with jsErrors: false</t>
         </is>
       </c>
       <c r="Q12" s="5" t="inlineStr">
